--- a/data/single_run/input/components/ambulances/amb_meisner.xlsx
+++ b/data/single_run/input/components/ambulances/amb_meisner.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>axp_1</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>axp_1</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>axp_1</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>axp_1</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>axp_2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>axp_2</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>axp_2</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>axp_2</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>axp_3</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>axp_3</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>axp_3</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C2_CCP_R1</t>
+          <t>C2_R1_R2</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>axp_3</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1335,420 +1335,6 @@
         <v>30</v>
       </c>
       <c r="E40" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AMB040</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>r1_14</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AMB041</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>r1_14</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>30</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AMB042</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>r1_14</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AMB043</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AMB044</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>30</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>AMB045</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" t="n">
-        <v>30</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AMB046</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>axp_1</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>30</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AMB047</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>axp_1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" t="n">
-        <v>30</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AMB048</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>axp_1</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>5</v>
-      </c>
-      <c r="D49" t="n">
-        <v>30</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AMB049</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>axp_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>30</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AMB050</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>axp_2</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>30</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AMB051</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>axp_2</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>5</v>
-      </c>
-      <c r="D52" t="n">
-        <v>30</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AMB052</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>axp_2</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>5</v>
-      </c>
-      <c r="D53" t="n">
-        <v>30</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AMB053</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>axp_2</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>5</v>
-      </c>
-      <c r="D54" t="n">
-        <v>30</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AMB054</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>axp_3</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>5</v>
-      </c>
-      <c r="D55" t="n">
-        <v>30</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AMB055</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>axp_3</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>5</v>
-      </c>
-      <c r="D56" t="n">
-        <v>30</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AMB056</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>axp_3</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>5</v>
-      </c>
-      <c r="D57" t="n">
-        <v>30</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AMB057</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>axp_3</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>30</v>
-      </c>
-      <c r="E58" t="inlineStr">
         <is>
           <t>C2_R1_R2</t>
         </is>
